--- a/demo/协作/ch01_frontend_alice.xlsx
+++ b/demo/协作/ch01_frontend_alice.xlsx
@@ -14,16 +14,18 @@
     <sheet name="Candidates_音乐" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Candidates_音效" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Candidates_语音" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="舞台快照" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="协作信息" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="词表" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="使用说明" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="舞台快照" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="协作信息" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="CAND_CHARACTER">=OFFSET('Candidates_角色'!$A$3,0,0,MAX(COUNTA('Candidates_角色'!$A$3:$A$5000),1),1)</definedName>
-    <definedName name="CAND_IMAGE">=OFFSET('Candidates_图片'!$A$3,0,0,MAX(COUNTA('Candidates_图片'!$A$3:$A$5000),1),1)</definedName>
-    <definedName name="CAND_TRANSFORM">=OFFSET('Candidates_变换'!$A$3,0,0,MAX(COUNTA('Candidates_变换'!$A$3:$A$5000),1),1)</definedName>
-    <definedName name="CAND_MUSIC">=OFFSET('Candidates_音乐'!$A$3,0,0,MAX(COUNTA('Candidates_音乐'!$A$3:$A$5000),1),1)</definedName>
-    <definedName name="CAND_SOUND">=OFFSET('Candidates_音效'!$A$3,0,0,MAX(COUNTA('Candidates_音效'!$A$3:$A$5000),1),1)</definedName>
-    <definedName name="CAND_VOICE">=OFFSET('Candidates_语音'!$A$3,0,0,MAX(COUNTA('Candidates_语音'!$A$3:$A$5000),1),1)</definedName>
+    <definedName name="CAND_CHARACTER">OFFSET('Candidates_角色'!$A$3,0,0,MAX(COUNTA('Candidates_角色'!$A$3:$A$5000),1),1)</definedName>
+    <definedName name="CAND_IMAGE">OFFSET('Candidates_图片'!$A$3,0,0,MAX(COUNTA('Candidates_图片'!$A$3:$A$5000),1),1)</definedName>
+    <definedName name="CAND_TRANSFORM">OFFSET('Candidates_变换'!$A$3,0,0,MAX(COUNTA('Candidates_变换'!$A$3:$A$5000),1),1)</definedName>
+    <definedName name="CAND_MUSIC">OFFSET('Candidates_音乐'!$A$3,0,0,MAX(COUNTA('Candidates_音乐'!$A$3:$A$5000),1),1)</definedName>
+    <definedName name="CAND_SOUND">OFFSET('Candidates_音效'!$A$3,0,0,MAX(COUNTA('Candidates_音效'!$A$3:$A$5000),1),1)</definedName>
+    <definedName name="CAND_VOICE">OFFSET('Candidates_语音'!$A$3,0,0,MAX(COUNTA('Candidates_语音'!$A$3:$A$5000),1),1)</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -69,11 +71,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -440,166 +443,130 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="52" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="30" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
+    <col width="32" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
-    <col width="26" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LineId</t>
+          <t>行号</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Seq</t>
+          <t>序号</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>章节</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>类型</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Comment</t>
+          <t>说话人</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Kind</t>
+          <t>注释</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>台词</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>背景</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>立绘</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Show</t>
+          <t>位置</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Hide</t>
+          <t>转场</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>At</t>
+          <t>退场</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>With</t>
+          <t>音乐</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Transform</t>
+          <t>音乐参数</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>StageOrder</t>
+          <t>音效</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>音效参数</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CodeBlock</t>
+          <t>语音</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Music</t>
+          <t>舞台（高级）</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>MusicParams</t>
+          <t>代码</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>MusicAction</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Sound</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>SoundParams</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>SoundAction</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Voice</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>ContentHash</t>
+          <t>内容指纹</t>
         </is>
       </c>
     </row>
@@ -617,64 +584,44 @@
           <t>ch01</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>say</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t># 表情A6，距离近</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>say</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>早上好，昨晚睡得好吗？</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>早上好，昨晚睡得好吗？</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
           <t>bg classroom</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>eileen happy@leftish</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>scene,show</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>[音乐] night fadein 1.0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>night</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>fadein 1.0</t>
+          <t>[显示] 爱莲 开心 at leftish</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>play</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>play</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>e55edfddf8</t>
+          <t>c6269f73be</t>
         </is>
       </c>
     </row>
@@ -692,44 +639,34 @@
           <t>ch01</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>say</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
           <t>还行，就是雨下了一整晚。</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>[音效] door</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>v_eileen_01</t>
+        </is>
+      </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>play</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>door</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>play</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>v_eileen_01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>04d7405dfa</t>
+          <t>c511132611</t>
         </is>
       </c>
     </row>
@@ -747,64 +684,44 @@
           <t>ch01</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>say</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
           <t>别想了，今天我们还有正事。</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>eileen sad@leftish; mary smile@right</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>eileen</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>hide,show</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>[音乐] rain fadeout 2.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>[显示] 爱莲 难过 at leftish; [显示] 玛丽 笑 右</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>with dissolve</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>rain</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>fadeout 2.0</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>play</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>play</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>17c8fe0577</t>
+          <t>a793eae740</t>
         </is>
       </c>
     </row>
@@ -822,595 +739,60 @@
           <t>ch01</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>say</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>[停止音乐]</t>
+        </is>
+      </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>play</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>39b7c73016</t>
+          <t>7ec99c88bb</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="11">
-    <dataValidation sqref="G2:G200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="未登记的资产" error="请从下拉列表中选择已登记的资产" promptTitle="Speaker" prompt="从资产表中选择（候选表新增的资产会自动出现）" type="list">
+  <dataValidations count="10">
+    <dataValidation sqref="E2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="说话人" prompt="从角色表选（也可直接写角色变量名）" type="list">
       <formula1>CAND_CHARACTER</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="未登记的资产" error="请从下拉列表中选择已登记的资产" promptTitle="Scene" prompt="从资产表中选择（候选表新增的资产会自动出现）" type="list">
+    <dataValidation sqref="H2:H200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="背景" prompt="从图片表选背景；要变换写 图@变换" type="list">
       <formula1>CAND_IMAGE</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="未登记的资产" error="请从下拉列表中选择已登记的资产" promptTitle="Show" prompt="从资产表中选择（候选表新增的资产会自动出现）" type="list">
+    <dataValidation sqref="I2:I200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="立绘" prompt="从图片表选立绘；多个用 ; 分隔；要位置写 图@变换" type="list">
       <formula1>CAND_IMAGE</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="未登记的资产" error="请从下拉列表中选择已登记的资产" promptTitle="At" prompt="从资产表中选择（候选表新增的资产会自动出现）" type="list">
+    <dataValidation sqref="J2:J200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="位置" prompt="位置变换（立绘用）" type="list">
       <formula1>CAND_TRANSFORM</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="未登记的资产" error="请从下拉列表中选择已登记的资产" promptTitle="With" prompt="从资产表中选择（候选表新增的资产会自动出现）" type="list">
+    <dataValidation sqref="K2:K200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="转场" prompt="转场效果" type="list">
       <formula1>CAND_TRANSFORM</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="未登记的资产" error="请从下拉列表中选择已登记的资产" promptTitle="Transform" prompt="从资产表中选择（候选表新增的资产会自动出现）" type="list">
-      <formula1>CAND_TRANSFORM</formula1>
+    <dataValidation sqref="L2:L200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="退场" prompt="要退场的立绘/图像；带转场写 图@转场" type="list">
+      <formula1>CAND_IMAGE</formula1>
     </dataValidation>
-    <dataValidation sqref="R2:R200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="未登记的资产" error="请从下拉列表中选择已登记的资产" promptTitle="Music" prompt="从资产表中选择（候选表新增的资产会自动出现）" type="list">
+    <dataValidation sqref="M2:M200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="音乐" prompt="从音乐表选；停止/排队请选伪值" type="list">
       <formula1>CAND_MUSIC</formula1>
     </dataValidation>
-    <dataValidation sqref="U2:U200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="未登记的资产" error="请从下拉列表中选择已登记的资产" promptTitle="Sound" prompt="从资产表中选择（候选表新增的资产会自动出现）" type="list">
+    <dataValidation sqref="O2:O200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="音效" prompt="从音效表选；停止/排队请选伪值" type="list">
       <formula1>CAND_SOUND</formula1>
     </dataValidation>
-    <dataValidation sqref="X2:X200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="未登记的资产" error="请从下拉列表中选择已登记的资产" promptTitle="Voice" prompt="从资产表中选择（候选表新增的资产会自动出现）" type="list">
+    <dataValidation sqref="Q2:Q200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="语音" prompt="从语音表选" type="list">
       <formula1>CAND_VOICE</formula1>
     </dataValidation>
-    <dataValidation sqref="T2:T200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="MusicAction" prompt="播放方式：play / queue / stop" type="list">
-      <formula1>"play,queue,stop"</formula1>
-    </dataValidation>
-    <dataValidation sqref="W2:W200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="SoundAction" prompt="播放方式：play / queue / stop" type="list">
-      <formula1>"play,queue,stop"</formula1>
+    <dataValidation sqref="D2:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="类型" prompt="say=角色说话 / narration=旁白 / menu=菜单提示 / menu_option=菜单选项 / extend=接着上一句" type="list">
+      <formula1>"say,narration,menu,menu_option,extend"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>↓ 本表是资源表的镜像（images/music/sounds/voices/transforms/characters）。A 列是可选值，B 列是说明；新增资产请先在资源表登记，再到编辑器点【刷新候选】。</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>参数/路径</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>爱莲 · #c8ffc8 · 立绘 eileen · 语音 eileen · 台词 1 · 定义于 ch01.rpy:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>玛丽 · #ffc8c8 · 立绘 mary · 台词 2 · 定义于 ch01.rpy:3</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>↓ 本表是资源表的镜像（images/music/sounds/voices/transforms/characters）。A 列是可选值，B 列是说明；新增资产请先在资源表登记，再到编辑器点【刷新候选】。</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>参数/路径</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>bg_classroom</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>背景 · tag=bg · 属性=bg_classroom · game/images/bg/bg_classroom.png</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>game/images/bg/bg_classroom.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>bg_rooftop</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>背景 · tag=bg · 属性=bg_rooftop · game/images/bg/bg_rooftop.png</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>game/images/bg/bg_rooftop.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>happy</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>其他 · tag=eileen · 属性=happy · game/images/eileen/happy.png</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>game/images/eileen/happy.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>happy_blush</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>其他 · tag=eileen · 属性=happy_blush · game/images/eileen/happy_blush.png</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>game/images/eileen/happy_blush.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>sad</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>其他 · tag=eileen · 属性=sad · game/images/eileen/sad.png</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>game/images/eileen/sad.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>smile</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>其他 · tag=mary · 属性=smile · game/images/mary/smile.png</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>game/images/mary/smile.png</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>↓ 本表是资源表的镜像（images/music/sounds/voices/transforms/characters）。A 列是可选值，B 列是说明；新增资产请先在资源表登记，再到编辑器点【刷新候选】。</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>参数/路径</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>fade_in_soft</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>柔和淡入，用于回忆切入 · custom · ATL 2 行</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>leftish</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>靠左站，双人对话时主角在左 · custom · ATL 2 行</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>shake_hard</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>剧烈抖动，挨打/惊吓演出用 · 参数 t=0.05, n=6 · custom · ATL 5 行</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>t=0.05, n=6</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>↓ 本表是资源表的镜像（images/music/sounds/voices/transforms/characters）。A 列是可选值，B 列是说明；新增资产请先在资源表登记，再到编辑器点【刷新候选】。</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>参数/路径</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>bgm_night</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>game/music/night.ogg · 循环 · 音量 1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>game/music/night.ogg</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>bgm_rain</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>game/music/rain.ogg · 循环 · 音量 1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>game/music/rain.ogg</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>↓ 本表是资源表的镜像（images/music/sounds/voices/transforms/characters）。A 列是可选值，B 列是说明；新增资产请先在资源表登记，再到编辑器点【刷新候选】。</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>参数/路径</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>sfx_click</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>game/sounds/click.ogg</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>game/sounds/click.ogg</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>sfx_door</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>game/sounds/door.ogg</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>game/sounds/door.ogg</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>↓ 本表是资源表的镜像（images/music/sounds/voices/transforms/characters）。A 列是可选值，B 列是说明；新增资产请先在资源表登记，再到编辑器点【刷新候选】。</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>参数/路径</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>v_eileen_01</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>game/voice/v_eileen_01.ogg</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>game/voice/v_eileen_01.ogg</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>v_eileen_02</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>game/voice/v_eileen_02.ogg</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>game/voice/v_eileen_02.ogg</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1433,57 +815,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>LineId</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Seq</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>说话人</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>台词</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>背景</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>立绘（谁·在哪）</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>音乐</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>音效</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>语音</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -1520,7 +902,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>eileen happy@leftish</t>
+          <t>爱莲 happy@leftish</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1560,7 +942,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>eileen happy@leftish</t>
+          <t>爱莲 happy@leftish</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1615,7 +997,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>eileen sad@leftish; mary smile@right</t>
+          <t>爱莲 sad@leftish; 玛丽 smile@right</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1625,7 +1007,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>原始语句</t>
+          <t>代码块</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1032,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>eileen sad@leftish; mary smile@right</t>
+          <t>爱莲 sad@leftish; 玛丽 smile@right</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1041,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1730,7 +1112,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-27T00:08:10</t>
+          <t>2026-09-27T16:45:53</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1138,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-27T00:08:10</t>
+          <t>2026-09-27T16:45:53</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1164,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-27T00:08:10</t>
+          <t>2026-09-27T16:45:53</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1190,2199 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-27T00:08:10</t>
+          <t>2026-09-27T16:45:53</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>↓ 本表是编译器的符号表（Symbol Table），由资源表镜像而来。A 列 = 策划能写的资产 ID，B 列 = 说明，C 列 = 真实路径。新增资产请先在资源表登记，再到编辑器点【刷新候选】。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>参数/路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>爱莲 · #c8ffc8 · 立绘 eileen · 语音 eileen · 台词 1 · 定义于 ch01.rpy:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>玛丽 · #ffc8c8 · 立绘 mary · 台词 2 · 定义于 ch01.rpy:3</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>↓ 本表是编译器的符号表（Symbol Table），由资源表镜像而来。A 列 = 策划能写的资产 ID，B 列 = 说明，C 列 = 真实路径。新增资产请先在资源表登记，再到编辑器点【刷新候选】。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>参数/路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>bg_classroom</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>背景 · tag=bg · 属性=bg_classroom · game/images/bg/bg_classroom.png</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>game/images/bg/bg_classroom.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bg_rooftop</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>背景 · tag=bg · 属性=bg_rooftop · game/images/bg/bg_rooftop.png</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>game/images/bg/bg_rooftop.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>其他 · tag=eileen · 属性=happy · game/images/eileen/happy.png</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>game/images/eileen/happy.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>happy_blush</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>其他 · tag=eileen · 属性=happy_blush · game/images/eileen/happy_blush.png</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>game/images/eileen/happy_blush.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sad</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>其他 · tag=eileen · 属性=sad · game/images/eileen/sad.png</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>game/images/eileen/sad.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>smile</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>其他 · tag=mary · 属性=smile · game/images/mary/smile.png</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>game/images/mary/smile.png</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>↓ 本表是编译器的符号表（Symbol Table），由资源表镜像而来。A 列 = 策划能写的资产 ID，B 列 = 说明，C 列 = 真实路径。新增资产请先在资源表登记，再到编辑器点【刷新候选】。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>参数/路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>fade_in_soft</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>柔和淡入，用于回忆切入 · custom · ATL 2 行</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>leftish</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>靠左站，双人对话时主角在左 · custom · ATL 2 行</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>shake_hard</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>剧烈抖动，挨打/惊吓演出用 · 参数 t=0.05, n=6 · custom · ATL 5 行</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>t=0.05, n=6</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>↓ 本表是编译器的符号表（Symbol Table），由资源表镜像而来。A 列 = 策划能写的资产 ID，B 列 = 说明，C 列 = 真实路径。新增资产请先在资源表登记，再到编辑器点【刷新候选】。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>参数/路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>（停止音乐）</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>动作：stop（不播放具体音频）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>（排队播放）</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>动作：queue（不播放具体音频）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bgm_night</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>game/music/night.ogg · 循环 · 音量 1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>game/music/night.ogg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>bgm_rain</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>game/music/rain.ogg · 循环 · 音量 1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>game/music/rain.ogg</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>↓ 本表是编译器的符号表（Symbol Table），由资源表镜像而来。A 列 = 策划能写的资产 ID，B 列 = 说明，C 列 = 真实路径。新增资产请先在资源表登记，再到编辑器点【刷新候选】。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>参数/路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>（停止音效）</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>动作：stop（不播放具体音频）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>（排队播放）</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>动作：queue（不播放具体音频）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sfx_click</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>game/sounds/click.ogg</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>game/sounds/click.ogg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sfx_door</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>game/sounds/door.ogg</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>game/sounds/door.ogg</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>↓ 本表是编译器的符号表（Symbol Table），由资源表镜像而来。A 列 = 策划能写的资产 ID，B 列 = 说明，C 列 = 真实路径。新增资产请先在资源表登记，再到编辑器点【刷新候选】。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>参数/路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>v_eileen_01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>game/voice/v_eileen_01.ogg</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>game/voice/v_eileen_01.ogg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>v_eileen_02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>game/voice/v_eileen_02.ogg</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>game/voice/v_eileen_02.ogg</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D63"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>↓ 这里的词可以直接写进 Beats 的 Stage / BGM / SFX 列。写错不会被拦，但生成的脚本里会出现 # TODO 注释。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>可写的词</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>会变成</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>爱莲</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>image eileen</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>[显示] 爱莲 开心 左 → show eileen …</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>玛丽</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>image mary</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>[显示] 玛丽 开心 左 → show mary …</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>不动</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>（不加 at）</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>[显示] 角色 开心 不动</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>at center</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[显示] 角色 开心 中</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>中央</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>at center</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>[显示] 角色 开心 中央</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>中间</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>at center</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>[显示] 角色 开心 中间</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>原地</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>（不加 at）</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>[显示] 角色 开心 原地</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>右</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>at right</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>[显示] 角色 开心 右</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>右侧</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>at right</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>[显示] 角色 开心 右侧</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>右边</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>at right</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>[显示] 角色 开心 右边</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>居中</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>at center</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>[显示] 角色 开心 居中</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>at left</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>[显示] 角色 开心 左</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>左侧</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>at left</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>[显示] 角色 开心 左侧</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>左边</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>at left</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>[显示] 角色 开心 左边</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>左边点</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>at left</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>[显示] 角色 开心 左边点</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>特写</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>at closeup</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>[显示] 角色 开心 特写</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>近</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>at close</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>[显示] 角色 开心 近</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>近处</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>at close</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>[显示] 角色 开心 近处</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>远</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>at far</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>[显示] 角色 开心 远</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>远处</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>at far</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>[显示] 角色 开心 远处</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表情</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>严肃</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>serious</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>按该角色的候选属性模糊匹配（开心 → close_happy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表情</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>伤心</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>sad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>按该角色的候选属性模糊匹配（开心 → close_happy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表情</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>叹气</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>sigh</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>按该角色的候选属性模糊匹配（开心 → close_happy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表情</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>吃惊</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>surprised</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>按该角色的候选属性模糊匹配（开心 → close_happy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表情</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>哭</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>cry</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>按该角色的候选属性模糊匹配（开心 → close_happy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表情</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>大笑</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>laugh</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>按该角色的候选属性模糊匹配（开心 → close_happy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表情</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>害羞</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>blush</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>按该角色的候选属性模糊匹配（开心 → close_happy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表情</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>常态</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>按该角色的候选属性模糊匹配（开心 → close_happy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表情</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>平静</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>按该角色的候选属性模糊匹配（开心 → close_happy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表情</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>开心</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>按该角色的候选属性模糊匹配（开心 → close_happy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表情</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>微笑</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>smile</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>按该角色的候选属性模糊匹配（开心 → close_happy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表情</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>快乐</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>按该角色的候选属性模糊匹配（开心 → close_happy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表情</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>怒</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>angry</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>按该角色的候选属性模糊匹配（开心 → close_happy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表情</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>悲伤</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>sad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>按该角色的候选属性模糊匹配（开心 → close_happy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表情</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>惊讶</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>surprised</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>按该角色的候选属性模糊匹配（开心 → close_happy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表情</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>愤怒</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>angry</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>按该角色的候选属性模糊匹配（开心 → close_happy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表情</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>无奈</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>sigh</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>按该角色的候选属性模糊匹配（开心 → close_happy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表情</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>无语</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>sigh</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>按该角色的候选属性模糊匹配（开心 → close_happy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表情</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>按该角色的候选属性模糊匹配（开心 → close_happy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表情</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>生气</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>angry</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>按该角色的候选属性模糊匹配（开心 → close_happy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表情</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>睁眼</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>按该角色的候选属性模糊匹配（开心 → close_happy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表情</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>笑</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>smile</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>按该角色的候选属性模糊匹配（开心 → close_happy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表情</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>脸红</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>blush</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>按该角色的候选属性模糊匹配（开心 → close_happy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表情</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>认真</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>serious</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>按该角色的候选属性模糊匹配（开心 → close_happy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表情</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>闭眼</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>按该角色的候选属性模糊匹配（开心 → close_happy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表情</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>难过</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>sad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>按该角色的候选属性模糊匹配（开心 → close_happy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表情</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>高兴</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>按该角色的候选属性模糊匹配（开心 → close_happy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>转场</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>dissolve</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>with dissolve</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>[转场] dissolve</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>转场</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>fade</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>with fade</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>[转场] fade</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>转场</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>fadeblack</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>with fadeblack</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>[转场] fadeblack</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>转场</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>fadewhite</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>with fadewhite</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>[转场] fadewhite</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>转场</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>pixellate</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>with pixellate</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>[转场] pixellate</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>转场</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>move</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>with move</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>[转场] move</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>转场</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ease</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>with ease</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>[转场] ease</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>转场</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>wipeleft</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>with wipeleft</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>[转场] wipeleft</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>转场</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>wiperight</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>with wiperight</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>[转场] wiperight</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>转场</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>irisin</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>with irisin</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>[转场] irisin</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>转场</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>irisout</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>with irisout</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>[转场] irisout</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>变换</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>leftish</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>at leftish</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>项目自定义变换（transforms.xlsx）</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>变换</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>shake_hard</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>at shake_hard</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>项目自定义变换（transforms.xlsx）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>变换</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>fade_in_soft</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>at fade_in_soft</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>项目自定义变换（transforms.xlsx）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="78" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>演出表怎么填（策划只看 Beats 这一张）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>一、三列写演出：</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Stage  舞台：出场 / 退场 / 换背景 / 转场 / 等待</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  BGM    音乐：播放、淡入淡出、停止</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SFX    音效：播放、停止</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>二、写法（多条用 ; 或换行分开）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [显示] 凌跃捷 开心 左          → show ling close_happy at left</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [显示] 凌跃捷 开心 左 with dissolve  → 带转场出场</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [隐藏] 凌跃捷                  → hide ling</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [场景] 实验室 with dissolve    → scene bg 实验室 with dissolve</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [转场] dissolve               → with dissolve</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [等待] 1.0                    → pause 1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [音乐] 春天花瓣 fadein 1.0     → play music "bgm/…" fadein 1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [停止音乐]                    → stop music</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [音效] 开门                   → play sound "sfx/…"</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  位置词可省略；表情可写多个（凌跃捷 开心 侧身）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>三、程序写复杂演出的后门：CodeBlock 列</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  里面写什么就原封不动抄进脚本，不解析、不校验。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  例：renpy.transition(Dissolve(0.1), layer="master")</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>四、找不到资源会怎样？</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  不报错、不中断。生成的脚本里会出现一行 # TODO: 缺少资源 …，</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  那句话不会生成（避免游戏运行时报错），其余照常生成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>五、原生写法也能写（程序/老策划习惯）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  直接写 show ling close_happy at left，编译器原样直通、不做解析。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>六、其他工作表</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  舞台快照    每句话时舞台上是什么样（自动算，只读）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Export_RenPy 编译结果（由工具生成，不要手改）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Candidates_* 编译器的符号表，不是给策划读的</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  词表        能写在 Stage 里的全部词</t>
         </is>
       </c>
     </row>

--- a/demo/协作/ch01_frontend_alice.xlsx
+++ b/demo/协作/ch01_frontend_alice.xlsx
@@ -16,8 +16,11 @@
     <sheet name="Candidates_语音" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="词表" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="使用说明" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="舞台快照" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="协作信息" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="资源图库" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="舞台快照" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="演出时间轴" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="列说明" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="协作信息" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="CAND_CHARACTER">OFFSET('Candidates_角色'!$A$3,0,0,MAX(COUNTA('Candidates_角色'!$A$3:$A$5000),1),1)</definedName>
@@ -26,6 +29,8 @@
     <definedName name="CAND_MUSIC">OFFSET('Candidates_音乐'!$A$3,0,0,MAX(COUNTA('Candidates_音乐'!$A$3:$A$5000),1),1)</definedName>
     <definedName name="CAND_SOUND">OFFSET('Candidates_音效'!$A$3,0,0,MAX(COUNTA('Candidates_音效'!$A$3:$A$5000),1),1)</definedName>
     <definedName name="CAND_VOICE">OFFSET('Candidates_语音'!$A$3,0,0,MAX(COUNTA('Candidates_语音'!$A$3:$A$5000),1),1)</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Beats'!$A$1:$T$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'演出时间轴'!$A$1:$F$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -34,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +50,23 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00555555"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+    </font>
+    <font>
+      <color rgb="00909090"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007F4F00"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -56,6 +76,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,12 +101,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -446,29 +500,29 @@
   <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="40" customWidth="1" min="18" max="18"/>
-    <col width="32" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="36" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>行号</t>
@@ -570,7 +624,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="45" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
           <t>ch01.0001</t>
@@ -621,11 +675,11 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>c6269f73be</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>40567d95ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
           <t>ch01.0002</t>
@@ -666,11 +720,11 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>c511132611</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>ce4c17e26e</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
           <t>ch01.0003</t>
@@ -714,18 +768,13 @@
           <t>[显示] 爱莲 难过 at leftish; [显示] 玛丽 笑 右</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>with dissolve</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>a793eae740</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+          <t>513d542f95</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
           <t>ch01.0004</t>
@@ -751,11 +800,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>7ec99c88bb</t>
+          <t>3ff3c503e2</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:T5"/>
   <dataValidations count="10">
     <dataValidation sqref="E2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="说话人" prompt="从角色表选（也可直接写角色变量名）" type="list">
       <formula1>CAND_CHARACTER</formula1>
@@ -798,250 +848,1496 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>↓ 资源图库：由资源表 + 脚本自动生成，**只读**（改这里没用，请改资源表）。「引用次数」= 脚本里用到几次，0 表示还没人用。界面/系统资源统一放在最后一段，策划通常不用管。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>▌背景　（2 项）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ID（可直接写进表格）</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>真实文件</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>引用次数</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>贴图预览</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>bg_classroom</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>背景 · tag=bg · 属性=bg_classroom · game/images/bg/bg_classroom.png</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>game/images/bg/bg_classroom.png</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>bg_rooftop</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>背景 · tag=bg · 属性=bg_rooftop · game/images/bg/bg_rooftop.png</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>game/images/bg/bg_rooftop.png</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>▌其他图　（4 项）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>ID（可直接写进表格）</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>真实文件</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>引用次数</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>贴图预览</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>其他 · tag=eileen · 属性=happy · game/images/eileen/happy.png</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>game/images/eileen/happy.png</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>happy_blush</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>其他 · tag=eileen · 属性=happy_blush · game/images/eileen/happy_blush.png</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>game/images/eileen/happy_blush.png</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>sad</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>其他 · tag=eileen · 属性=sad · game/images/eileen/sad.png</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>game/images/eileen/sad.png</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>smile</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>其他 · tag=mary · 属性=smile · game/images/mary/smile.png</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>game/images/mary/smile.png</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>▌音乐　（2 项）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>ID（可直接写进表格）</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>真实文件</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>引用次数</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>贴图预览</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>bgm_night</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>game/music/night.ogg · 循环 · 音量 1</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>game/music/night.ogg</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>bgm_rain</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>game/music/rain.ogg · 循环 · 音量 1</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>game/music/rain.ogg</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>▌音效　（2 项）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ID（可直接写进表格）</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>真实文件</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>引用次数</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>贴图预览</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>sfx_click</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>game/sounds/click.ogg</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>game/sounds/click.ogg</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>sfx_door</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>game/sounds/door.ogg</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>game/sounds/door.ogg</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>▌语音　（2 项）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>ID（可直接写进表格）</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>真实文件</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>引用次数</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>贴图预览</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>v_eileen_01</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>game/voice/v_eileen_01.ogg</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>game/voice/v_eileen_01.ogg</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>v_eileen_02</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>game/voice/v_eileen_02.ogg</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>game/voice/v_eileen_02.ogg</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>▌自定义变换　（3 项）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>ID（可直接写进表格）</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>真实文件</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>引用次数</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>贴图预览</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>fade_in_soft</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>柔和淡入，用于回忆切入 · custom · ATL 2 行</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>leftish</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>靠左站，双人对话时主角在左 · custom · ATL 2 行</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>shake_hard</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>剧烈抖动，挨打/惊吓演出用 · 参数 t=0.05, n=6 · custom · ATL 5 行</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>LineId</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Seq</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>章节</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>说话人</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>台词</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>本拍变化</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>背景</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>立绘（谁·在哪）</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CG·图层</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>音乐</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>音效</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>语音</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="45" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>ch01.0001</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>ch01</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>早上好，昨晚睡得好吗？</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>+ 爱莲 happy @ leftish（登场）
+♪ 音乐 → night fadein 1.0
+背景 → bg classroom</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>bg classroom</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>爱莲 happy@leftish</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr"/>
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr"/>
+      <c r="L2" s="7" t="inlineStr"/>
+      <c r="M2" s="7" t="inlineStr"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>ch01.0002</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>ch01</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>还行，就是雨下了一整晚。</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>♫ 音效 door
+🎙 语音 v_eileen_01</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>bg classroom</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>爱莲 happy@leftish</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr"/>
+      <c r="J3" s="10" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>door</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>v_eileen_01</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" s="7" t="inlineStr">
         <is>
           <t>音效 door</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>ch01.0003</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>ch01</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>别想了，今天我们还有正事。</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>+ 爱莲 sad @ leftish（登场）
++ 玛丽 smile @ right（登场）
+♪ 音乐 → rain fadeout 2.0</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>bg classroom</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" s="9" t="inlineStr">
         <is>
           <t>爱莲 sad@leftish; 玛丽 smile@right</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr"/>
+      <c r="J4" s="9" t="inlineStr">
         <is>
           <t>rain</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>代码块</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr"/>
+      <c r="L4" s="7" t="inlineStr"/>
+      <c r="M4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>ch01.0004</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>ch01</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>♪ 停止音乐</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>bg classroom</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>爱莲 sad@leftish; 玛丽 smile@right</t>
         </is>
       </c>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="9" t="inlineStr"/>
+      <c r="K5" s="7" t="inlineStr"/>
+      <c r="L5" s="7" t="inlineStr"/>
+      <c r="M5" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>LineId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Seq</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>章节</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>说话人</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>台词</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>本拍变化</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>ch01.0001</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>ch01</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>早上好，昨晚睡得好吗？</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>+ 爱莲 happy @ leftish（登场）
+♪ 音乐 → night fadein 1.0
+背景 → bg classroom</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>ch01.0002</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>ch01</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>还行，就是雨下了一整晚。</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>♫ 音效 door
+🎙 语音 v_eileen_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>ch01.0003</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>ch01</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>别想了，今天我们还有正事。</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>+ 爱莲 sad @ leftish（登场）
++ 玛丽 smile @ right（登场）
+♪ 音乐 → rain fadeout 2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>ch01.0004</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>ch01</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>♪ 停止音乐</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>列</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>属于</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>给谁看</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>怎么填</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>行号 LineId</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>程序区</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>协作/追溯</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>自动生成，别改</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>序号 Seq</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>程序区</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>排序</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>自动生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>章节 Label</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>这一行属于哪个 label</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>类型 Kind</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>下拉：说话/旁白/菜单/菜单选项/延续</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>说话人 Speaker</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>下拉选角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>注释 Comment</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>给自己/同事看的备注，会写进脚本注释</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>台词 Text</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>这一句台词</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>背景 Scene</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>下拉选背景；`图@变换` 可带背景变换</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>立绘 Show</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>下拉选图；`图@位置` 指定站位</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>位置 At</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>没用 @ 指定站位的立绘统一用这列</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>转场 With</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>下拉选转场</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>退场 Hide</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>下拉选图；`图@转场` 可带退场转场</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>音乐 BGM</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>下拉选音乐；也可选「（停止音乐）」</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>音乐参数 BGMParams</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>如 `fadein 1.0`</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>音效 SFX</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>下拉选音效；也可选「（停止音效）」</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>音效参数 SFXParams</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>如 `volume 0.5`</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>语音 Voice</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>下拉选语音</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>舞台（高级）Stage</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>高级区</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>策划（进阶）</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>结构化列表达不了的指令；人话或原生写法都行</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>代码 CodeBlock</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>程序区</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>程序</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>原样抄进脚本的逃生舱，不解析不校验</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>内容指纹 ContentHash</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>程序区</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>协作</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>自动重算，别改</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1112,7 +2408,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-27T16:45:53</t>
+          <t>2026-09-27T18:20:08</t>
         </is>
       </c>
     </row>
@@ -1138,7 +2434,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-27T16:45:53</t>
+          <t>2026-09-27T18:20:08</t>
         </is>
       </c>
     </row>
@@ -1164,7 +2460,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-27T16:45:53</t>
+          <t>2026-09-27T18:20:08</t>
         </is>
       </c>
     </row>
@@ -1190,7 +2486,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-27T16:45:53</t>
+          <t>2026-09-27T18:20:08</t>
         </is>
       </c>
     </row>

--- a/demo/协作/ch01_frontend_alice.xlsx
+++ b/demo/协作/ch01_frontend_alice.xlsx
@@ -29,7 +29,7 @@
     <definedName name="CAND_MUSIC">OFFSET('Candidates_音乐'!$A$3,0,0,MAX(COUNTA('Candidates_音乐'!$A$3:$A$5000),1),1)</definedName>
     <definedName name="CAND_SOUND">OFFSET('Candidates_音效'!$A$3,0,0,MAX(COUNTA('Candidates_音效'!$A$3:$A$5000),1),1)</definedName>
     <definedName name="CAND_VOICE">OFFSET('Candidates_语音'!$A$3,0,0,MAX(COUNTA('Candidates_语音'!$A$3:$A$5000),1),1)</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Beats'!$A$1:$T$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Beats'!$A$1:$V$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'演出时间轴'!$A$1:$F$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -520,6 +520,8 @@
     <col width="36" customWidth="1" min="18" max="18"/>
     <col width="30" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
+    <col hidden="1" width="16" customWidth="1" min="21" max="21"/>
+    <col hidden="1" width="16" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -623,6 +625,16 @@
           <t>内容指纹</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>舞台顺序（内部）</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>操作顺序（内部）</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="45" customHeight="1">
       <c r="A2" t="inlineStr">
@@ -663,19 +675,19 @@
           <t>bg classroom</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>eileen happy@leftish</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>[音乐] night fadein 1.0</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>[显示] 爱莲 开心 at leftish</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>40567d95ff</t>
+          <t>30e3677233</t>
         </is>
       </c>
     </row>
@@ -753,6 +765,11 @@
           <t>别想了，今天我们还有正事。</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>eileen sad@leftish; mary smile@right</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>eileen</t>
@@ -763,14 +780,9 @@
           <t>[音乐] rain fadeout 2.0</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>[显示] 爱莲 难过 at leftish; [显示] 玛丽 笑 右</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>513d542f95</t>
+          <t>fc0058395e</t>
         </is>
       </c>
     </row>
@@ -805,7 +817,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T5"/>
+  <autoFilter ref="A1:V5"/>
   <dataValidations count="10">
     <dataValidation sqref="E2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="说话人" prompt="从角色表选（也可直接写角色变量名）" type="list">
       <formula1>CAND_CHARACTER</formula1>
@@ -1503,7 +1515,7 @@
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>+ 爱莲 happy @ leftish（登场）
+          <t>+ eileen happy @ leftish（登场）
 ♪ 音乐 → night fadein 1.0
 背景 → bg classroom</t>
         </is>
@@ -1515,7 +1527,7 @@
       </c>
       <c r="H2" s="9" t="inlineStr">
         <is>
-          <t>爱莲 happy@leftish</t>
+          <t>eileen happy@leftish</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr"/>
@@ -1565,7 +1577,7 @@
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>爱莲 happy@leftish</t>
+          <t>eileen happy@leftish</t>
         </is>
       </c>
       <c r="I3" s="7" t="inlineStr"/>
@@ -1590,7 +1602,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1">
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>ch01.0003</t>
@@ -1616,8 +1628,9 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>+ 爱莲 sad @ leftish（登场）
-+ 玛丽 smile @ right（登场）
+          <t>+ eileen sad @ leftish（登场）
++ mary smile @ right（登场）
+− eileen（退场）
 ♪ 音乐 → rain fadeout 2.0</t>
         </is>
       </c>
@@ -1628,7 +1641,7 @@
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
-          <t>爱莲 sad@leftish; 玛丽 smile@right</t>
+          <t>mary smile@right</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr"/>
@@ -1669,7 +1682,7 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>爱莲 sad@leftish; 玛丽 smile@right</t>
+          <t>mary smile@right</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr"/>
@@ -1758,7 +1771,7 @@
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>+ 爱莲 happy @ leftish（登场）
+          <t>+ eileen happy @ leftish（登场）
 ♪ 音乐 → night fadein 1.0
 背景 → bg classroom</t>
         </is>
@@ -1795,7 +1808,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1">
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>ch01.0003</t>
@@ -1821,8 +1834,9 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>+ 爱莲 sad @ leftish（登场）
-+ 玛丽 smile @ right（登场）
+          <t>+ eileen sad @ leftish（登场）
++ mary smile @ right（登场）
+− eileen（退场）
 ♪ 音乐 → rain fadeout 2.0</t>
         </is>
       </c>
@@ -2408,7 +2422,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-27T18:20:08</t>
+          <t>2026-09-28T16:16:27</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2448,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-27T18:20:08</t>
+          <t>2026-09-28T16:16:27</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2474,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-27T18:20:08</t>
+          <t>2026-09-28T16:16:27</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2500,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-27T18:20:08</t>
+          <t>2026-09-28T16:16:27</t>
         </is>
       </c>
     </row>

--- a/demo/协作/ch01_frontend_alice.xlsx
+++ b/demo/协作/ch01_frontend_alice.xlsx
@@ -2422,7 +2422,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-28T16:16:27</t>
+          <t>2026-09-28T21:13:36</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-28T16:16:27</t>
+          <t>2026-09-28T21:13:36</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-28T16:16:27</t>
+          <t>2026-09-28T21:13:36</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-28T16:16:27</t>
+          <t>2026-09-28T21:13:36</t>
         </is>
       </c>
     </row>
